--- a/saida_skus/SKU_UTD-038-ORGANIZADOR-GAVETA-EXTENSIVEL-MADEIRA.xlsx
+++ b/saida_skus/SKU_UTD-038-ORGANIZADOR-GAVETA-EXTENSIVEL-MADEIRA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 580,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,14 +1082,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,8 +1120,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1130,39 +1132,41 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1193,10 +1197,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1205,39 +1207,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1273,9 +1273,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,14 +1382,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1421,11 +1421,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1448,19 +1448,19 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,14 +1682,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1720,10 +1720,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1732,39 +1730,37 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1836,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1990,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2067,12 +2063,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2144,12 +2140,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2221,12 +2217,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2298,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2375,12 +2371,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,12 +2448,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2529,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2606,12 +2602,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2683,12 +2679,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2760,12 +2756,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2837,12 +2833,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2914,12 +2910,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2991,12 +2987,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3068,12 +3064,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3145,12 +3141,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3222,12 +3218,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3299,12 +3295,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3376,12 +3372,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3453,12 +3449,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3530,12 +3526,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3607,12 +3603,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3684,12 +3680,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3761,12 +3757,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3838,12 +3834,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3915,12 +3911,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3992,12 +3988,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4069,12 +4065,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4146,12 +4142,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4223,12 +4219,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4300,12 +4296,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4377,12 +4373,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4454,12 +4450,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4531,12 +4527,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4608,12 +4604,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4685,12 +4681,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4762,12 +4758,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4839,12 +4835,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4916,12 +4912,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4993,12 +4989,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5070,12 +5066,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5147,12 +5143,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5224,12 +5220,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5301,12 +5297,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5378,12 +5374,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5455,12 +5451,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5532,12 +5528,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5609,12 +5605,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5686,12 +5682,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5763,12 +5759,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5840,12 +5836,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5917,12 +5913,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5994,12 +5990,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6071,12 +6067,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6148,12 +6144,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6225,12 +6221,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6302,12 +6298,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6379,12 +6375,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6456,12 +6452,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6533,12 +6529,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6610,12 +6606,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6687,12 +6683,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6764,12 +6760,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6841,12 +6837,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6918,12 +6914,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6995,12 +6991,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7072,12 +7068,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7149,12 +7145,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7226,12 +7222,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7303,12 +7299,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7380,12 +7376,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7457,12 +7453,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7534,12 +7530,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7611,12 +7607,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7688,12 +7684,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7765,12 +7761,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7842,12 +7838,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7919,12 +7915,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7996,12 +7992,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8073,12 +8069,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8150,12 +8146,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8227,12 +8223,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8304,12 +8300,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8381,12 +8377,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8458,12 +8454,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8535,12 +8531,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8612,12 +8608,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8689,12 +8685,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8766,12 +8762,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8843,12 +8839,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8920,12 +8916,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8997,12 +8993,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9074,12 +9070,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9151,12 +9147,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9228,12 +9224,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9305,12 +9301,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9382,12 +9378,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9459,12 +9455,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9536,12 +9532,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9613,12 +9609,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9690,12 +9686,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9767,12 +9763,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9844,12 +9840,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9921,12 +9917,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9998,12 +9994,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10075,12 +10071,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10152,12 +10148,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10229,12 +10225,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10306,12 +10302,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10383,12 +10379,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10460,12 +10456,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10537,12 +10533,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10614,12 +10610,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10691,12 +10687,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10768,12 +10764,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10845,12 +10841,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10922,12 +10918,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10999,12 +10995,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11076,12 +11072,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11153,12 +11149,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11230,12 +11226,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11307,12 +11303,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11384,12 +11380,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11461,12 +11457,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11538,12 +11534,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11615,12 +11611,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11692,12 +11688,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11769,12 +11765,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11846,12 +11842,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11923,12 +11919,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -12000,12 +11996,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12077,12 +12073,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12154,12 +12150,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12231,12 +12227,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12308,12 +12304,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12385,12 +12381,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12462,12 +12458,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12539,12 +12535,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12616,12 +12612,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12693,12 +12689,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12770,12 +12766,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12847,12 +12843,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12924,12 +12920,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -13001,12 +12997,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -13078,12 +13074,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -13155,12 +13151,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13232,12 +13228,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13309,12 +13305,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13386,82 +13382,236 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4786362859</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-038</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Organizador Gaveta extensivel madeira</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>6993953494</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4786362859</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-038-ORGANIZADOR-GAVETA-EXTENSIVEL-MADEIRA.xlsx
+++ b/saida_skus/SKU_UTD-038-ORGANIZADOR-GAVETA-EXTENSIVEL-MADEIRA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 580,0%</t>
+          <t>▼ 55,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -748,24 +748,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>34</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 580,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,14 +1232,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1270,8 +1270,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1280,39 +1282,41 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1343,10 +1347,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1355,39 +1357,37 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1423,9 +1423,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,14 +1532,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1598,19 +1598,19 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1832,14 +1832,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1870,10 +1870,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1882,39 +1880,37 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1986,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2140,12 +2136,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2217,12 +2213,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2294,12 +2290,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2371,12 +2367,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2448,12 +2444,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2525,12 +2521,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,12 +2598,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2679,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2756,12 +2752,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2833,12 +2829,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2910,12 +2906,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2987,12 +2983,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3064,12 +3060,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3141,12 +3137,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3218,12 +3214,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3295,12 +3291,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3372,12 +3368,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3449,12 +3445,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3526,12 +3522,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3603,12 +3599,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3680,12 +3676,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3757,12 +3753,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3834,12 +3830,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3911,12 +3907,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3988,12 +3984,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4065,12 +4061,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4142,12 +4138,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4219,12 +4215,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4296,12 +4292,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4373,12 +4369,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4450,12 +4446,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4527,12 +4523,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4604,12 +4600,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4681,12 +4677,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4758,12 +4754,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4835,12 +4831,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4912,12 +4908,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4989,12 +4985,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5066,12 +5062,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5143,12 +5139,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5220,12 +5216,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5297,12 +5293,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5374,12 +5370,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5451,12 +5447,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5528,12 +5524,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5605,12 +5601,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5682,12 +5678,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5759,12 +5755,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5836,12 +5832,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5913,12 +5909,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5990,12 +5986,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6067,12 +6063,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6144,12 +6140,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6221,12 +6217,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6298,12 +6294,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6375,12 +6371,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6452,12 +6448,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6529,12 +6525,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6606,12 +6602,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6683,12 +6679,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6760,12 +6756,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6837,12 +6833,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6914,12 +6910,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6991,12 +6987,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7068,12 +7064,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7145,12 +7141,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7222,12 +7218,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7299,12 +7295,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7376,12 +7372,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7453,12 +7449,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7530,12 +7526,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7607,12 +7603,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7684,12 +7680,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7761,12 +7757,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7838,12 +7834,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7915,12 +7911,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7992,12 +7988,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8069,12 +8065,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8146,12 +8142,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8223,12 +8219,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8300,12 +8296,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8377,12 +8373,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8454,12 +8450,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8531,12 +8527,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8608,12 +8604,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8685,12 +8681,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8762,12 +8758,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8839,12 +8835,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8916,12 +8912,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8993,12 +8989,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9070,12 +9066,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9147,12 +9143,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9224,12 +9220,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9301,12 +9297,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9378,12 +9374,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9455,12 +9451,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9532,12 +9528,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9609,12 +9605,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9686,12 +9682,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9763,12 +9759,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9840,12 +9836,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9917,12 +9913,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9994,12 +9990,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10071,12 +10067,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10148,12 +10144,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10225,12 +10221,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10302,12 +10298,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10379,12 +10375,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10456,12 +10452,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10533,12 +10529,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10610,12 +10606,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10687,12 +10683,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10764,12 +10760,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10841,12 +10837,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10918,12 +10914,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10995,12 +10991,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11072,12 +11068,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11149,12 +11145,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11226,12 +11222,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11303,12 +11299,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11380,12 +11376,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11457,12 +11453,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11534,12 +11530,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11611,12 +11607,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11688,12 +11684,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11765,12 +11761,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11842,12 +11838,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11919,12 +11915,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11996,12 +11992,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12073,12 +12069,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12150,12 +12146,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12227,12 +12223,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12304,12 +12300,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12381,12 +12377,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12458,12 +12454,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12535,12 +12531,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12612,12 +12608,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12689,12 +12685,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12766,12 +12762,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12843,12 +12839,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12920,12 +12916,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12997,12 +12993,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -13074,12 +13070,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -13151,12 +13147,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13228,12 +13224,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13305,12 +13301,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13382,12 +13378,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13459,12 +13455,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13536,82 +13532,236 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4786362859</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-038</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Organizador Gaveta extensivel madeira</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>6993953494</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4786362859</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-038-ORGANIZADOR-GAVETA-EXTENSIVEL-MADEIRA.xlsx
+++ b/saida_skus/SKU_UTD-038-ORGANIZADOR-GAVETA-EXTENSIVEL-MADEIRA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,9%</t>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 580,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,24 +898,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 580,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,14 +1382,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1420,8 +1420,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1430,39 +1432,41 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1485,7 +1489,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1493,10 +1497,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1505,39 +1507,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1573,9 +1573,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,14 +1682,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -1721,11 +1721,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1748,19 +1748,19 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1982,14 +1982,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-038</t>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2020,10 +2020,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2032,39 +2030,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2136,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2213,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2290,12 +2286,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2367,12 +2363,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2444,12 +2440,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2521,12 +2517,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2598,12 +2594,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2675,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2752,12 +2748,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2829,12 +2825,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2906,12 +2902,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2983,12 +2979,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3060,12 +3056,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3137,12 +3133,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3214,12 +3210,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3291,12 +3287,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3368,12 +3364,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3445,12 +3441,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3522,12 +3518,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3599,12 +3595,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3676,12 +3672,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3753,12 +3749,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3830,12 +3826,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3907,12 +3903,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3984,12 +3980,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4061,12 +4057,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4138,12 +4134,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4215,12 +4211,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4292,12 +4288,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4369,12 +4365,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4446,12 +4442,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4523,12 +4519,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4600,12 +4596,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4677,12 +4673,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4754,12 +4750,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4831,12 +4827,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4908,12 +4904,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4985,12 +4981,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5062,12 +5058,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5139,12 +5135,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5216,12 +5212,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5293,12 +5289,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5370,12 +5366,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5447,12 +5443,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5524,12 +5520,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5601,12 +5597,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5678,12 +5674,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5755,12 +5751,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5832,12 +5828,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5909,12 +5905,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5986,12 +5982,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6063,12 +6059,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6140,12 +6136,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6217,12 +6213,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6294,12 +6290,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6371,12 +6367,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6448,12 +6444,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6525,12 +6521,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6602,12 +6598,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6679,12 +6675,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6756,12 +6752,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6833,12 +6829,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6910,12 +6906,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6987,12 +6983,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7064,12 +7060,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7141,12 +7137,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7218,12 +7214,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7295,12 +7291,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7372,12 +7368,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7449,12 +7445,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7526,12 +7522,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7603,12 +7599,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7680,12 +7676,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7757,12 +7753,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7834,12 +7830,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7911,12 +7907,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7988,12 +7984,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8065,12 +8061,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8142,12 +8138,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8219,12 +8215,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8296,12 +8292,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8373,12 +8369,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8450,12 +8446,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8527,12 +8523,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8604,12 +8600,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8681,12 +8677,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8758,12 +8754,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8835,12 +8831,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8912,12 +8908,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8989,12 +8985,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9066,12 +9062,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9143,12 +9139,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9220,12 +9216,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9297,12 +9293,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9374,12 +9370,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9451,12 +9447,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9528,12 +9524,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9605,12 +9601,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9682,12 +9678,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9759,12 +9755,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9836,12 +9832,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9913,12 +9909,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9990,12 +9986,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10067,12 +10063,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10144,12 +10140,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10221,12 +10217,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10298,12 +10294,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10375,12 +10371,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10452,12 +10448,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10529,12 +10525,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10606,12 +10602,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10683,12 +10679,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10760,12 +10756,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10837,12 +10833,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10914,12 +10910,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10991,12 +10987,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11068,12 +11064,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11145,12 +11141,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11222,12 +11218,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11299,12 +11295,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11376,12 +11372,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11453,12 +11449,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11530,12 +11526,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11607,12 +11603,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11684,12 +11680,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11761,12 +11757,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11838,12 +11834,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11915,12 +11911,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11992,12 +11988,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12069,12 +12065,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12146,12 +12142,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12223,12 +12219,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12300,12 +12296,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12377,12 +12373,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12454,12 +12450,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12531,12 +12527,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12608,12 +12604,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12685,12 +12681,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12762,12 +12758,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12839,12 +12835,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12916,12 +12912,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12993,12 +12989,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -13070,12 +13066,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -13147,12 +13143,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13224,12 +13220,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13301,12 +13297,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13378,12 +13374,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13455,12 +13451,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13532,12 +13528,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13609,12 +13605,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13686,82 +13682,236 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4786362859</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-038</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Organizador Gaveta extensivel madeira</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>6993953494</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4786362859</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-038-ORGANIZADOR-GAVETA-EXTENSIVEL-MADEIRA.xlsx
+++ b/saida_skus/SKU_UTD-038-ORGANIZADOR-GAVETA-EXTENSIVEL-MADEIRA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 133,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 125,4%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,7%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,51 +670,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -812,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -820,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -832,39 +826,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,16 +890,16 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 580,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 566,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -915,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1040,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1151,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1342,17 +1334,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 55,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1451,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,7 +1481,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1498,24 +1490,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 580,0%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1562,7 +1554,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1570,8 +1562,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1580,37 +1574,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1635,7 +1631,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1643,51 +1639,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1712,7 +1704,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1720,47 +1712,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1793,51 +1789,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1862,7 +1854,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1870,47 +1862,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>1</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1935,7 +1931,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1943,51 +1939,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2012,7 +2004,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2020,8 +2012,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>1</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2030,37 +2024,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2085,7 +2081,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2093,10 +2089,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2105,39 +2099,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2162,7 +2154,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2170,10 +2162,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2182,39 +2172,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2286,12 +2274,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2316,7 +2304,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2324,51 +2312,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2440,12 +2424,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2470,7 +2454,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2478,51 +2462,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2594,12 +2574,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2624,7 +2604,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2632,10 +2612,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2644,39 +2622,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2748,12 +2724,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2825,12 +2801,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2902,12 +2878,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2979,12 +2955,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3056,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3133,12 +3109,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3210,12 +3186,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3287,12 +3263,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3364,12 +3340,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3441,12 +3417,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3518,12 +3494,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3595,12 +3571,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3672,12 +3648,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3749,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3826,12 +3802,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3903,12 +3879,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3980,12 +3956,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4057,12 +4033,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4134,12 +4110,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4211,12 +4187,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4288,12 +4264,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4365,12 +4341,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4442,12 +4418,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4519,12 +4495,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4596,12 +4572,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4673,12 +4649,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4750,12 +4726,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4827,12 +4803,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4904,12 +4880,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4981,12 +4957,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5058,12 +5034,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5135,12 +5111,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5212,12 +5188,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5289,12 +5265,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5366,12 +5342,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5443,12 +5419,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5520,12 +5496,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5597,12 +5573,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5674,12 +5650,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5751,12 +5727,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5828,12 +5804,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5905,12 +5881,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5982,12 +5958,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6059,12 +6035,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6136,12 +6112,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6213,12 +6189,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6290,12 +6266,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6367,12 +6343,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6444,12 +6420,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6521,12 +6497,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6598,12 +6574,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6675,12 +6651,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6752,12 +6728,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6829,12 +6805,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6906,12 +6882,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6983,12 +6959,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7060,12 +7036,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7137,12 +7113,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7214,12 +7190,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7291,12 +7267,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7368,12 +7344,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7445,12 +7421,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7522,12 +7498,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7599,12 +7575,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7676,12 +7652,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7753,12 +7729,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7830,12 +7806,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7907,12 +7883,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7984,12 +7960,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8061,12 +8037,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8138,12 +8114,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8215,12 +8191,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8292,12 +8268,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8369,12 +8345,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8446,12 +8422,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8523,12 +8499,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8600,12 +8576,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8677,12 +8653,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8754,12 +8730,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8831,12 +8807,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8908,12 +8884,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8985,12 +8961,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9062,12 +9038,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9139,12 +9115,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9216,12 +9192,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9293,12 +9269,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9370,12 +9346,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9447,12 +9423,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9524,12 +9500,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9601,12 +9577,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9678,12 +9654,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9755,12 +9731,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9832,12 +9808,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9909,12 +9885,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9986,12 +9962,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10063,12 +10039,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10140,12 +10116,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10217,12 +10193,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10294,12 +10270,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10371,12 +10347,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10448,12 +10424,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10525,12 +10501,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10602,12 +10578,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10679,12 +10655,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10756,12 +10732,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10833,12 +10809,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10910,12 +10886,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10987,12 +10963,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11064,12 +11040,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11141,12 +11117,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11218,12 +11194,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11295,12 +11271,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11372,12 +11348,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11449,12 +11425,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11526,12 +11502,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11603,12 +11579,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11680,12 +11656,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11757,12 +11733,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11834,12 +11810,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11911,12 +11887,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11988,12 +11964,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12065,12 +12041,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12142,12 +12118,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12219,12 +12195,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12296,12 +12272,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12373,12 +12349,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12450,12 +12426,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12527,12 +12503,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12604,12 +12580,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12681,12 +12657,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12758,12 +12734,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12835,12 +12811,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12912,12 +12888,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12989,12 +12965,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -13066,12 +13042,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -13143,12 +13119,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13220,12 +13196,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13297,12 +13273,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13374,12 +13350,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13451,12 +13427,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13528,12 +13504,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13605,12 +13581,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13682,12 +13658,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13759,12 +13735,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13836,82 +13812,698 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4786362859</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>6993953494</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4786362859</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>6993953494</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4786362859</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>6993953494</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4786362859</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-038</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Organizador Gaveta extensivel madeira</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>6993953494</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-038</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Gaveta extensivel madeira</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4786362859</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>